--- a/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno4/anno4_task2_user_chatbot_emotion.xlsx
+++ b/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno4/anno4_task2_user_chatbot_emotion.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD94CE25-E735-4426-BF02-26558ECB3014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B33470-0CCA-444F-A10A-454E71742441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="347">
   <si>
     <t>UID</t>
   </si>
@@ -56,46 +56,46 @@
     <t>COMMENTS</t>
   </si>
   <si>
-    <t>SFTANNO-000188-0002</t>
-  </si>
-  <si>
-    <t>I discovered a local farmer's market and have been buying all my produce there!</t>
-  </si>
-  <si>
-    <t>It's scary to think about the long-term impact of unsustainable food production methods.</t>
-  </si>
-  <si>
-    <t>It's important to continue supporting local farmers and sustainable food options to prevent the negative impacts of industrial agriculture.</t>
-  </si>
-  <si>
-    <t>Just be cautious of food waste and try to plan meals accordingly.</t>
-  </si>
-  <si>
-    <t>While it's great that you're making sustainable choices, it's also important to be aware of the environmental impact of food production and how we can make choices that reduce our carbon footprint.</t>
-  </si>
-  <si>
-    <t>While it's great to support local farmers, it's important to also be aware of the impact of large-scale agriculture on the environment.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000184-0002</t>
-  </si>
-  <si>
-    <t>The Dyatlov Pass Incident is so creepy, it sends shivers down my spine.</t>
-  </si>
-  <si>
-    <t>It's scary to think about the unknown forces that could have been at play in that incident.</t>
-  </si>
-  <si>
-    <t>It's truly frightening to think about what could have happened to them.</t>
-  </si>
-  <si>
-    <t>It's terrifying to think about what could have happened to those hikers in the wilderness.</t>
-  </si>
-  <si>
-    <t>It's scary to think that something like that could happen to anyone.</t>
-  </si>
-  <si>
-    <t>It's scary to think about what could happen to us when we're out in the wilderness.</t>
+    <t>SFTANNO-000034-0002</t>
+  </si>
+  <si>
+    <t>Yes, there are some interesting options that I'm considering.</t>
+  </si>
+  <si>
+    <t>But remember to always do your research and be cautious about potential scams or fraudulent investments.</t>
+  </si>
+  <si>
+    <t>But make sure to do your research and understand the risks involved before making any decisions.</t>
+  </si>
+  <si>
+    <t>Just remember that investing always carries some level of risk, so it's important to be cautious and do your research.</t>
+  </si>
+  <si>
+    <t>Just be cautious and do your research before investing in anything.</t>
+  </si>
+  <si>
+    <t>Just make sure to do your research and invest wisely. The market can be unpredictable.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000171-0002</t>
+  </si>
+  <si>
+    <t>Not really. I wanted to try some fancy French cuisine, but couldn't afford it.</t>
+  </si>
+  <si>
+    <t>I'm happy to hear you had a great time exploring the city. What were some of your favorite sights?</t>
+  </si>
+  <si>
+    <t>I loved getting a croissant and coffee every morning. It was the perfect way to start the day.</t>
+  </si>
+  <si>
+    <t>I'm glad you got to experience some of the local culture, and I hope you got to try some delicious French bread at least.</t>
+  </si>
+  <si>
+    <t>I had a great time trying out some of the street food and crepes!</t>
+  </si>
+  <si>
+    <t>But I heard that there are some great local cafes and bakeries in Paris that offer delicious French pastries and sandwiches.</t>
   </si>
   <si>
     <t>SFTANNO-000025-0002</t>
@@ -119,487 +119,508 @@
     <t>I'm surprised at how much better you're feeling about the situation.</t>
   </si>
   <si>
-    <t>SFTANNO-000008-0002</t>
-  </si>
-  <si>
-    <t>I've been thinking about volunteering at an animal shelter. It's a cause that's close to my heart.</t>
-  </si>
-  <si>
-    <t>I'm sorry to hear that animal shelters are still needed.</t>
-  </si>
-  <si>
-    <t>It's heartbreaking to see so many animals in need.</t>
-  </si>
-  <si>
-    <t>What motivated you to want to volunteer at a shelter?</t>
-  </si>
-  <si>
-    <t>How do you think you can make a difference?</t>
-  </si>
-  <si>
-    <t>It's so sad to think about the number of animals in need.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000195-0002</t>
-  </si>
-  <si>
-    <t>I haven't, but I'm also afraid that what I visualize won't look as good in reality.</t>
-  </si>
-  <si>
-    <t>It's important to consider the overall aesthetic of your apartment and how the furniture fits into that vision.</t>
-  </si>
-  <si>
-    <t>Visualizing can be helpful, but don't forget to consider other factors like comfort and functionality as well.</t>
-  </si>
-  <si>
-    <t>You could try looking at furniture in person or taking photos of the options to get a better idea of how it will look.</t>
-  </si>
-  <si>
-    <t>It's important to think about the space and how the furniture will fit and flow.</t>
-  </si>
-  <si>
-    <t>It's always good to have a plan and try to make it work, even if it's not perfect.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000021-0002</t>
-  </si>
-  <si>
-    <t>Have you heard about the possibility of black holes existing at the beginning of the universe?</t>
-  </si>
-  <si>
-    <t>But at the same time, it's a bit scary to think about the unknown aspects of black holes that we still don't understand.</t>
-  </si>
-  <si>
-    <t>But at the same time, it's also a little scary to think about the possibilities.</t>
-  </si>
-  <si>
-    <t>But at the same time, it's scary to think about how much we still don't know about the universe and how it came to be.</t>
-  </si>
-  <si>
-    <t>But it's also a bit scary to think about the idea of black holes being present at the very beginning of the universe.</t>
-  </si>
-  <si>
-    <t>It's scary to think about how much we still don't know about the universe and what kind of dangers might be lurking out there.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000054-0002</t>
-  </si>
-  <si>
-    <t>I'm really into rap music, especially conscious hip-hop that tackles social issues.</t>
-  </si>
-  <si>
-    <t>I was surprised to find out how much I enjoyed listening to conscious hip-hop, it's really powerful.</t>
-  </si>
-  <si>
-    <t>I recently discovered a rap song that has a really positive message, I was surprised to find something that I enjoyed.</t>
-  </si>
-  <si>
-    <t>I was surprised to hear that you enjoy conscious hip-hop, I'm always interested in learning more about different genres.</t>
-  </si>
-  <si>
-    <t>I didn't expect to find someone else who appreciates conscious hip-hop, I thought it was a niche genre.</t>
-  </si>
-  <si>
-    <t>I'm surprised that you're into conscious hip-hop, it's not as mainstream as other rap genres.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000029-0002</t>
-  </si>
-  <si>
-    <t>I can't stand when fashion magazines promote unrealistic body images.</t>
-  </si>
-  <si>
-    <t>Have you seen any fashion magazines lately?</t>
-  </si>
-  <si>
-    <t>How do you think we can promote more inclusive fashion media?</t>
-  </si>
-  <si>
-    <t>What do you think can be done to combat those harmful messages?</t>
-  </si>
-  <si>
-    <t>What do you think about the fashion industry's influence on body image?</t>
-  </si>
-  <si>
-    <t>Do you have any favorite fashion magazines that promote body positivity?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000052-0002</t>
-  </si>
-  <si>
-    <t>I wish I had learned to play an instrument when I was younger.</t>
-  </si>
-  <si>
-    <t>I'm afraid I won't have the time or patience to learn now.</t>
-  </si>
-  <si>
-    <t>I'm afraid of not being able to learn, but I know it's possible.</t>
-  </si>
-  <si>
-    <t>But I'm afraid I don't have the time to dedicate to it.</t>
-  </si>
-  <si>
-    <t>It can be scary to start something new, but I'm here to support you.</t>
-  </si>
-  <si>
-    <t>It's scary to think about learning something new, but it's also really exciting!</t>
-  </si>
-  <si>
-    <t>SFTANNO-000020-0002</t>
-  </si>
-  <si>
-    <t>I worry that exploring black holes could be dangerous for us and for our machines.</t>
-  </si>
-  <si>
-    <t>I'm surprised you're open to the possibility of new discoveries, but it's definitely worth considering.</t>
-  </si>
-  <si>
-    <t>But I'm surprised by how much we've been able to learn about black holes already, despite the dangers.</t>
-  </si>
-  <si>
-    <t>I'm surprised that scientists have been able to gather so much data about black holes despite the dangers involved.</t>
-  </si>
-  <si>
-    <t>It's surprising to think about the possibilities for exploration and discovery that come with understanding black holes.</t>
-  </si>
-  <si>
-    <t>It's surprising to think about the potential for discovery, though. Who knows what we could learn from studying black holes?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000129-0002</t>
-  </si>
-  <si>
-    <t>One study I read showed that genetic modification can have unintended consequences on the ecosystem if not properly managed.</t>
-  </si>
-  <si>
-    <t>It's important to continue researching and implementing ethical guidelines to ensure the safety of our environment and food supply.</t>
-  </si>
-  <si>
-    <t>It's important to weigh the potential benefits against the potential risks and implement proper regulations and oversight.</t>
-  </si>
-  <si>
-    <t>It's important to make sure that any genetic modification is done in a responsible and ethical manner.</t>
-  </si>
-  <si>
-    <t>It's important to ensure that any new genetic modifications are thoroughly tested for potential negative impacts.</t>
-  </si>
-  <si>
-    <t>It's important to approach genetic modification with caution and proper oversight to minimize any potential negative impacts.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000093-0002</t>
-  </si>
-  <si>
-    <t>Yes, I changed all my passwords and notified everyone about the phone loss.</t>
-  </si>
-  <si>
-    <t>It's always better to be safe than sorry, and you're taking the right steps to protect your information.</t>
-  </si>
-  <si>
-    <t>It's important to take those precautions to protect your information and accounts.</t>
-  </si>
-  <si>
-    <t>It's important to be cautious with our personal information. Do you have a spare phone you can use until you get a new one?</t>
-  </si>
-  <si>
-    <t>I'm sorry that happened to you. Let me know if you need anything else.</t>
-  </si>
-  <si>
-    <t>Yeah, that's a smart move. You don't want to be a victim of identity theft.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000060-0002</t>
-  </si>
-  <si>
-    <t>With so many people relying on social media for their news, it's concerning how easy it is for false information to spread.</t>
-  </si>
-  <si>
-    <t>It's disheartening to see how some people choose to spread false information and manipulate others.</t>
-  </si>
-  <si>
-    <t>It's unfortunate how some people choose to spread false information for their own gain.</t>
-  </si>
-  <si>
-    <t>It's disgusting how people can spread false information without any consequences.</t>
-  </si>
-  <si>
-    <t>It's disgusting how some people use social media to spread false information for their own gain.</t>
-  </si>
-  <si>
-    <t>It's so frustrating how people can be so easily swayed by false information.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000185-0002</t>
-  </si>
-  <si>
-    <t>The Zodiac Killer is such a frustrating mystery.</t>
-  </si>
-  <si>
-    <t>I can't imagine how difficult it must have been for the families of the victims.</t>
-  </si>
-  <si>
-    <t>It's heartbreaking to think about the victims and their families who never got the closure they deserved.</t>
-  </si>
-  <si>
-    <t>It's really sad that they were never brought to justice and the families were left with so many unanswered questions.</t>
-  </si>
-  <si>
-    <t>It's sad to think that the victims and their families will never get the closure they deserve.</t>
-  </si>
-  <si>
-    <t>It's so sad to think about the families who were affected by the Zodiac Killer's actions.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000180-0002</t>
-  </si>
-  <si>
-    <t>I don't know, the idea of raw fish doesn't sound appetizing.</t>
-  </si>
-  <si>
-    <t>But don't worry, there are plenty of cooked sushi options too, like teriyaki rolls or tempura rolls.</t>
-  </si>
-  <si>
-    <t>Oh, you should try the tempura rolls! They're cooked and delicious.</t>
-  </si>
-  <si>
-    <t>But don't worry, they offer cooked options too! They have this amazing tempura roll that's cooked to perfection.</t>
-  </si>
-  <si>
-    <t>I'm surprised you wouldn't want to try it. But if you don't like raw fish, there are plenty of other great Japanese restaurants to try.</t>
-  </si>
-  <si>
-    <t>Did you know that sushi rice is made with vinegar and sugar? It's actually really tasty.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000049-0002</t>
-  </si>
-  <si>
-    <t>The director just announced a new initiative, and I'm genuinely surprised.</t>
-  </si>
-  <si>
-    <t>But I'm not sure I like the sound of it.</t>
-  </si>
-  <si>
-    <t>It's not a surprise that the director is always coming up with new initiatives.</t>
-  </si>
-  <si>
-    <t>It's surprising, but I'm not sure if it's a good idea.</t>
-  </si>
-  <si>
-    <t>I'm concerned about the direction this initiative is taking.</t>
-  </si>
-  <si>
-    <t>I'm surprised, but it sounds like something the director would do.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000175-0002</t>
-  </si>
-  <si>
-    <t>We'll need apples, cinnamon, flour, sugar, butter, and lemon.</t>
-  </si>
-  <si>
-    <t>The only thing I'm not sure about is the lemon, but I'm willing to give it a shot.</t>
-  </si>
-  <si>
-    <t>Just one question, why do we need lemon in apple pie?</t>
-  </si>
-  <si>
-    <t>Ugh, I can't stand the smell of butter, it makes me sick.</t>
-  </si>
-  <si>
-    <t>Unfortunately, I don't have any lemons at home.</t>
-  </si>
-  <si>
-    <t>I hope it doesn't take too long to make, I'm getting hungry.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000005-0002</t>
-  </si>
-  <si>
-    <t>I'm so happy with my new prescription sunglasses. They make everything so much clearer!</t>
-  </si>
-  <si>
-    <t>I didn't even realize you needed new glasses, they look great on you!</t>
-  </si>
-  <si>
-    <t>Wow, that's awesome! I never realized how much clearer things could be with the right sunglasses.</t>
-  </si>
-  <si>
-    <t>I'm surprised how much of a difference it can make!</t>
-  </si>
-  <si>
-    <t>I didn't realize how much of a difference sunglasses could make.</t>
-  </si>
-  <si>
-    <t>I didn't know they could make such a big difference.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000046-0002</t>
-  </si>
-  <si>
-    <t>Yes, I tried boiling brussels sprouts, and they came out mushy.</t>
-  </si>
-  <si>
-    <t>I'm so afraid of undercooking or overcooking vegetables.</t>
-  </si>
-  <si>
-    <t>I'm afraid of ruining any vegetable I try to cook.</t>
-  </si>
-  <si>
-    <t>I'm afraid of ruining another vegetable dish. I don't know how to cook them.</t>
-  </si>
-  <si>
-    <t>I'm afraid of ruining vegetables in the same way.</t>
-  </si>
-  <si>
-    <t>I'm afraid of overcooking them. I might try grilling them instead.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000123-0002</t>
-  </si>
-  <si>
-    <t>No, I haven't, but I'm excited to try!</t>
-  </si>
-  <si>
-    <t>I'm sure you'll love it! Let me know how it turns out.</t>
-  </si>
-  <si>
-    <t>I hope you love it!</t>
-  </si>
-  <si>
-    <t>It's always fun to try new things in the kitchen.</t>
-  </si>
-  <si>
-    <t>I can't wait to hear how it goes!</t>
-  </si>
-  <si>
-    <t>It's always fun to try new recipes and ingredients.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000189-0002</t>
-  </si>
-  <si>
-    <t>I think it's possible, but it depends on their individual streaming preferences.</t>
-  </si>
-  <si>
-    <t>I'm glad we can agree on that. It's always great to find common ground.</t>
-  </si>
-  <si>
-    <t>But the beauty of it is that we can find what we like. It's like a personalized journey through entertainment.</t>
-  </si>
-  <si>
-    <t>It's nice to have different options for everyone to find their perfect streaming match.</t>
-  </si>
-  <si>
-    <t>That's why it's exciting when new platforms emerge and offer something different.</t>
-  </si>
-  <si>
-    <t>But I'm glad we can still enjoy our favorite shows and movies, regardless of the platform.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000125-0002</t>
-  </si>
-  <si>
-    <t>I do, actually. The leaves seem to clog our gutters every fall.</t>
-  </si>
-  <si>
-    <t>It's unfortunate that the trees can cause so much maintenance.</t>
-  </si>
-  <si>
-    <t>I'm sorry to hear that. It can be frustrating to deal with that every year.</t>
-  </si>
-  <si>
-    <t>It's unfortunate that the trees cause you so much trouble.</t>
-  </si>
-  <si>
-    <t>I'm sorry to hear that. Clogged gutters can lead to a lot of problems.</t>
-  </si>
-  <si>
-    <t>It's unfortunate that something as beautiful as trees can create so much work.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000010-0002</t>
-  </si>
-  <si>
-    <t>My pet rabbit passed away recently, and I'm struggling to cope with the loss.</t>
-  </si>
-  <si>
-    <t>It's a scary feeling when we lose a pet, isn't it? I hope you find comfort in your memories.</t>
-  </si>
-  <si>
-    <t>I can't imagine the pain you must be feeling. It's okay to grieve and take time to heal.</t>
-  </si>
-  <si>
-    <t>It's understandable to feel that way. Remember, you're not alone in your grief.</t>
-  </si>
-  <si>
-    <t>Losing a pet is devastating. It's okay to feel scared and unsure of how to cope.</t>
-  </si>
-  <si>
-    <t>It's a difficult time, and I hope you find solace in the memories you shared.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000117-0002</t>
-  </si>
-  <si>
-    <t>Yes, one recommendation stood out, and I'm surprised at how positive the feedback is.</t>
-  </si>
-  <si>
-    <t>It's unfortunate that finding the right doctor can be a challenging process.</t>
-  </si>
-  <si>
-    <t>I'm sorry you had to go through such a negative experience before finding a good doctor.</t>
-  </si>
-  <si>
-    <t>It's unfortunate that a negative experience has led you to this point.</t>
-  </si>
-  <si>
-    <t>I'm sorry you had to go through a bad experience, but I'm glad you're taking steps to improve it.</t>
-  </si>
-  <si>
-    <t>It's unfortunate that healthcare experiences can be disappointing.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000114-0002</t>
-  </si>
-  <si>
-    <t>I'm so glad to be leaving the hospital. I feel so much better.</t>
-  </si>
-  <si>
-    <t>It's great to hear you're feeling better. But I'm sorry to hear about your experience with the hospital.</t>
-  </si>
-  <si>
-    <t>It's a relief to be leaving the hospital, but I'm glad you're feeling better.</t>
-  </si>
-  <si>
-    <t>That's great to hear. But, I have to say, the hospital food is pretty terrible.</t>
-  </si>
-  <si>
-    <t>I'm glad you're feeling better, but I'm sorry you had to go through that.</t>
-  </si>
-  <si>
-    <t>It's unfortunate that you had to be in the hospital, but I'm glad you're feeling better now.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000032-0002</t>
-  </si>
-  <si>
-    <t>I just got a new watch that tracks my sleep patterns and heart rate!</t>
-  </si>
-  <si>
-    <t>I had no idea watches could do that! It's amazing how technology has evolved.</t>
-  </si>
-  <si>
-    <t>I didn't even know there were smartwatches that could track that kind of information!</t>
-  </si>
-  <si>
-    <t>Wow, that sounds like something out of a sci-fi movie!</t>
-  </si>
-  <si>
-    <t>I had no idea that watches could do all that. That's really impressive.</t>
-  </si>
-  <si>
-    <t>I had no idea watches could do that!</t>
+    <t>SFTANNO-000007-0002</t>
+  </si>
+  <si>
+    <t>They actually offered me the job!</t>
+  </si>
+  <si>
+    <t>Are you feeling overwhelmed by the new opportunity?</t>
+  </si>
+  <si>
+    <t>Wow, congratulations! What are your initial thoughts about the new job?</t>
+  </si>
+  <si>
+    <t>I'm happy for you, but now you have to think about the new job and the responsibilities that come with it.</t>
+  </si>
+  <si>
+    <t>Congratulations, but now comes the hard part: deciding if it's the right fit for you.</t>
+  </si>
+  <si>
+    <t>It's great news, but also scary, right?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000084-0002</t>
+  </si>
+  <si>
+    <t>My coach just retired, and I feel like I've lost a mentor.</t>
+  </si>
+  <si>
+    <t>But also, think of all the new opportunities and growth that lie ahead with a new coach.</t>
+  </si>
+  <si>
+    <t>But remember, you'll always have the skills and knowledge they taught you.</t>
+  </si>
+  <si>
+    <t>But don't let that fear hold you back from reaching out to the new coach and asking for guidance.</t>
+  </si>
+  <si>
+    <t>But remember, you have the skills and experience to continue growing as an athlete.</t>
+  </si>
+  <si>
+    <t>But don't worry, you can still find guidance and support from other sources, like your teammates and other coaches.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000156-0002</t>
+  </si>
+  <si>
+    <t>There are! You can start with small changes, like rearranging furniture or adding plants to boost the energy in your space.</t>
+  </si>
+  <si>
+    <t>I'm still a bit nervous about making changes, but I'm willing to try.</t>
+  </si>
+  <si>
+    <t>But I'm still a bit afraid to make any changes. What if I mess up?</t>
+  </si>
+  <si>
+    <t>But I'm still a bit afraid of making too many changes at once.</t>
+  </si>
+  <si>
+    <t>I'm just a bit nervous about messing up and not doing it right.</t>
+  </si>
+  <si>
+    <t>But I'm worried about keeping plants alive. Do you have any tips?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000167-0002</t>
+  </si>
+  <si>
+    <t>Do you think we'll see the implementation of AI in our daily lives soon?</t>
+  </si>
+  <si>
+    <t>I'm happy to see that AI can help us in our daily lives, like in our homes or even in our cars.</t>
+  </si>
+  <si>
+    <t>I'm thrilled to think about the possibilities that AI could bring to our daily lives, making them easier and more efficient.</t>
+  </si>
+  <si>
+    <t>I'm excited to see how AI will improve our daily lives and make things more efficient.</t>
+  </si>
+  <si>
+    <t>It's exciting to think about the possibilities and advancements that AI will bring to our daily lives.</t>
+  </si>
+  <si>
+    <t>I'm excited to see how AI can help us streamline our daily routines and make things more efficient.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000000-0002</t>
+  </si>
+  <si>
+    <t>You won't believe it! They killed off my favorite character, and I'm so mad about it!</t>
+  </si>
+  <si>
+    <t>That's understandable. How do you think the story will go on without them?</t>
+  </si>
+  <si>
+    <t>I understand how you feel. How did you cope with that loss?</t>
+  </si>
+  <si>
+    <t>It's definitely a bummer when that happens. Have you considered skipping the next book?</t>
+  </si>
+  <si>
+    <t>It's tough when a favorite character dies. How are you coping with it?</t>
+  </si>
+  <si>
+    <t>It can be disappointing when a beloved character is taken away. How did you react?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000182-0002</t>
+  </si>
+  <si>
+    <t>The Holocaust, because I want to understand how such devastation could happen.</t>
+  </si>
+  <si>
+    <t>It's a heavy topic, but understanding history is crucial for a better future.</t>
+  </si>
+  <si>
+    <t>Yes, understanding the past can help us avoid making the same mistakes in the future.</t>
+  </si>
+  <si>
+    <t>I agree, it's crucial to learn from history and its darker aspects.</t>
+  </si>
+  <si>
+    <t>It's a difficult subject, but important to understand.</t>
+  </si>
+  <si>
+    <t>It's a difficult but important period of history to learn about.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000004-0002</t>
+  </si>
+  <si>
+    <t>I'm worried about my son's eyesight. He's been complaining about headaches lately.</t>
+  </si>
+  <si>
+    <t>Have you considered taking him for an eye exam?</t>
+  </si>
+  <si>
+    <t>Maybe it's a good idea to schedule an appointment with an eye doctor.</t>
+  </si>
+  <si>
+    <t>I'm sure it's just a precautionary measure, but it's always better to be safe than sorry.</t>
+  </si>
+  <si>
+    <t>Have you considered taking him to an optometrist to get his eyes checked?</t>
+  </si>
+  <si>
+    <t>It's important to have him checked by an eye doctor as soon as possible.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000160-0002</t>
+  </si>
+  <si>
+    <t>Did you hear about that controversial moment at the awards show?</t>
+  </si>
+  <si>
+    <t>It's shocking how some people can't control their emotions in public.</t>
+  </si>
+  <si>
+    <t>It's shocking that someone could be so disrespectful in that setting.</t>
+  </si>
+  <si>
+    <t>I can't believe how some people still think that way.</t>
+  </si>
+  <si>
+    <t>I'm surprised they thought that would be acceptable to air on live TV.</t>
+  </si>
+  <si>
+    <t>I can't believe they let that happen in the first place.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000165-0002</t>
+  </si>
+  <si>
+    <t>I just heard about a close friend moving to a different country, and I'm really going to miss them.</t>
+  </si>
+  <si>
+    <t>But at the same time, you'll have new experiences and memories to create that you never would have had if you didn't move away.</t>
+  </si>
+  <si>
+    <t>But remember that they're just moving to a different country, not to another planet. It's not like you'll never see them again.</t>
+  </si>
+  <si>
+    <t>But it's also an exciting opportunity for them to explore new places and experiences.</t>
+  </si>
+  <si>
+    <t>But there's also excitement in new beginnings and the possibility of future adventures together.</t>
+  </si>
+  <si>
+    <t>But remember, even though they're far away, you can still stay connected through technology and visit them when you can.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000190-0002</t>
+  </si>
+  <si>
+    <t>I'm afraid I'm becoming addicted to binge-watching.</t>
+  </si>
+  <si>
+    <t>It's great to lose yourself in a good show. Have you discovered any new favorites lately?</t>
+  </si>
+  <si>
+    <t>But at the same time, it's a great way to escape reality for a while.</t>
+  </si>
+  <si>
+    <t>I understand your fear, but you've discovered some great shows!</t>
+  </si>
+  <si>
+    <t>Don't worry; it happens to the best of us. How do you usually manage your time when binge-watching?</t>
+  </si>
+  <si>
+    <t>It's great that you're aware of it. Maybe you can try setting limits or taking breaks.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000053-0002</t>
+  </si>
+  <si>
+    <t>I just found out that my friend's band is performing at a local venue tomorrow night.</t>
+  </si>
+  <si>
+    <t>That's such great news! You'll have a fantastic time at the show.</t>
+  </si>
+  <si>
+    <t>I'm so happy for you, supporting local music is always a great experience.</t>
+  </si>
+  <si>
+    <t>That sounds like such a fun night out! I hope you have a great time at the show!</t>
+  </si>
+  <si>
+    <t>I'm so excited to hear them play live! Let's go check it out.</t>
+  </si>
+  <si>
+    <t>That's so exciting, I hope you have a great time!</t>
+  </si>
+  <si>
+    <t>SFTANNO-000067-0002</t>
+  </si>
+  <si>
+    <t>I've tried, but there are so many sources out there with conflicting information that they trust the ones that align with their beliefs.</t>
+  </si>
+  <si>
+    <t>It's frustrating that some people refuse to consider the consequences of their actions and the potential harm they could cause to others.</t>
+  </si>
+  <si>
+    <t>It's disgusting that people can choose to believe whatever they want, even if it's not true, and put others' health at risk.</t>
+  </si>
+  <si>
+    <t>It's disgusting that people are willing to risk their health and others by refusing to vaccinate themselves and their children.</t>
+  </si>
+  <si>
+    <t>It's truly disgusting that people can easily fall for misinformation about vaccines, and it can have serious consequences for public health.</t>
+  </si>
+  <si>
+    <t>It's disgusting that some people prioritize their own beliefs over the health and safety of others.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000141-0002</t>
+  </si>
+  <si>
+    <t>I hope so, as long as it's used for ethical purposes.</t>
+  </si>
+  <si>
+    <t>It's a double-edged sword, with great potential for good, but also the risk of misuse.</t>
+  </si>
+  <si>
+    <t>It's definitely a technology that has the potential to be used for good or bad.</t>
+  </si>
+  <si>
+    <t>It's a double-edged sword, it has the potential to do a lot of good, but also a lot of harm.</t>
+  </si>
+  <si>
+    <t>Do you think there will ever be a point where VR is as common as regular video games?</t>
+  </si>
+  <si>
+    <t>Have you heard of any recent developments in VR technology?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000169-0002</t>
+  </si>
+  <si>
+    <t>Companies need to be held accountable for their security measures, and regulations need to be put in place to ensure that they are.</t>
+  </si>
+  <si>
+    <t>It might be helpful to look into how other countries regulate 5G security and see if there are any best practices that we can adopt.</t>
+  </si>
+  <si>
+    <t>It's important to keep the conversation going and advocate for better security measures.</t>
+  </si>
+  <si>
+    <t>It's a complex issue, but regulations can help ensure companies prioritize security alongside profit.</t>
+  </si>
+  <si>
+    <t>It's important to hold companies accountable for their security measures, and regulations could be a good way to ensure that they are taking proper measures.</t>
+  </si>
+  <si>
+    <t>It's important to have a balance between regulations and innovation to ensure that security measures are effective.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000001-0002</t>
+  </si>
+  <si>
+    <t>I finished that book you recommended, and it was amazing!</t>
+  </si>
+  <si>
+    <t>I hope I don't jinx it, but I'm a bit nervous about recommending another book to you.</t>
+  </si>
+  <si>
+    <t>I'm happy you liked it, but I'm a bit scared of not finding other books that you'll enjoy. What did you like about it?</t>
+  </si>
+  <si>
+    <t>I'm so happy you enjoyed it! However, I'm a bit afraid that my other recommendations won't live up to that one.</t>
+  </si>
+  <si>
+    <t>Now, what book should I recommend next? I'm afraid I'll disappoint you with my choice.</t>
+  </si>
+  <si>
+    <t>I'm thrilled to hear that, but I hope I haven't spoiled anything for you.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000161-0002</t>
+  </si>
+  <si>
+    <t>Honestly, I just can't believe the company would put us through this unnecessary anxiety and tension.</t>
+  </si>
+  <si>
+    <t>It's unacceptable. They need to be held accountable for their actions and be more transparent with their employees.</t>
+  </si>
+  <si>
+    <t>They should be held accountable for the way they handled this situation. It's completely unprofessional.</t>
+  </si>
+  <si>
+    <t>It's infuriating how they handled this. They should have been more open and considerate of their employees' feelings.</t>
+  </si>
+  <si>
+    <t>It's infuriating that they would treat their employees like this. We deserve better than this.</t>
+  </si>
+  <si>
+    <t>I'm angry that they would treat their employees this way. They should be held accountable for their actions.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000013-0002</t>
+  </si>
+  <si>
+    <t>I've never really thought about it, but I'm interested in exploring more.</t>
+  </si>
+  <si>
+    <t>It's unfortunate that ballet is often overlooked and underappreciated in our culture, but I'm glad you're interested in exploring it more.</t>
+  </si>
+  <si>
+    <t>It's unfortunate that ballet is often seen as elitist or only for a certain type of person, but it's really for everyone to enjoy.</t>
+  </si>
+  <si>
+    <t>Although I do think some ballets can be overly pretentious and snobbish, there are so many beautiful and unique stories that are worth exploring.</t>
+  </si>
+  <si>
+    <t>Although there are so many beautiful ballets out there, it's unfortunate that the industry can be so limiting and exclusive.</t>
+  </si>
+  <si>
+    <t>It's a shame that there's still a lot of stigma and misconceptions surrounding ballet, but I hope you find some beautiful performances that change your mind.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000155-0002</t>
+  </si>
+  <si>
+    <t>Not really. I'm not really that handy.</t>
+  </si>
+  <si>
+    <t>It's not fair that you have to make these changes. You shouldn't have to do all the work.</t>
+  </si>
+  <si>
+    <t>It's frustrating when you don't have the skills to make those changes. Have you considered hiring a professional?</t>
+  </si>
+  <si>
+    <t>It's not fair that you have to spend so much money and time on something that should be a happy inheritance.</t>
+  </si>
+  <si>
+    <t>It's ridiculous that we have to spend so much money to make everything work together.</t>
+  </si>
+  <si>
+    <t>It's frustrating that the furniture doesn't fit your style, but don't worry, we'll find a solution.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000055-0002</t>
+  </si>
+  <si>
+    <t>I really like the rhythm of the drums in African music.</t>
+  </si>
+  <si>
+    <t>I'm so happy to hear that you like African music, it's such a unique and exciting genre!</t>
+  </si>
+  <si>
+    <t>I feel so happy when I listen to African music because it always makes me want to dance.</t>
+  </si>
+  <si>
+    <t>African music is so diverse and rich in rhythm, it's always a joy to listen to.</t>
+  </si>
+  <si>
+    <t>I'm excited to explore African music now, I bet it has some great rhythms to dance to.</t>
+  </si>
+  <si>
+    <t>I love learning about different cultures and their music.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000099-0002</t>
+  </si>
+  <si>
+    <t>I have, but it still feels like such a big cost.</t>
+  </si>
+  <si>
+    <t>It's a lot of money to spend on a console, I worry about the long-term investment.</t>
+  </si>
+  <si>
+    <t>It's scary to think about spending so much money on a console, but the new games are so exciting.</t>
+  </si>
+  <si>
+    <t>I'm afraid I won't be able to afford it, but I hope to be able to soon.</t>
+  </si>
+  <si>
+    <t>It's tough to decide whether it's worth the investment.</t>
+  </si>
+  <si>
+    <t>I'm worried about the cost of games as well, it adds up quickly.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000002-0002</t>
+  </si>
+  <si>
+    <t>Not yet, everything is still uncertain due to the pandemic.</t>
+  </si>
+  <si>
+    <t>It's frustrating that the pandemic has caused so much uncertainty and loss in the industry.</t>
+  </si>
+  <si>
+    <t>It's frustrating how the pandemic has affected so many aspects of our lives, especially for those in creative fields.</t>
+  </si>
+  <si>
+    <t>It's frustrating how much the pandemic has disrupted the book industry and author events.</t>
+  </si>
+  <si>
+    <t>It's frustrating that the pandemic is still affecting so many aspects of our lives. I hope things get better soon.</t>
+  </si>
+  <si>
+    <t>It's frustrating that the pandemic is still affecting the industry. But I'm sure your book will still find its way to readers.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000149-0002</t>
+  </si>
+  <si>
+    <t>Certain personality types are often dismissed or overlooked in creative industries.</t>
+  </si>
+  <si>
+    <t>It's maddening that creativity is still so narrowly defined by personality types. We need to break down those stereotypes.</t>
+  </si>
+  <si>
+    <t>It's frustrating that certain personality types are still overlooked and underrepresented in creative fields. We need to work towards a more inclusive industry.</t>
+  </si>
+  <si>
+    <t>It's infuriating that certain personalities are not given the same opportunities in creative industries. We need to work towards a more inclusive and diverse industry.</t>
+  </si>
+  <si>
+    <t>It's unacceptable that certain personality types are often overlooked or dismissed in the creative industry. We need to continue to push for inclusivity and representation.</t>
+  </si>
+  <si>
+    <t>It's unacceptable how certain personality types are overlooked and not given equal opportunities.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000070-0002</t>
+  </si>
+  <si>
+    <t>Have you heard about the recent discovery of gravitational waves?</t>
+  </si>
+  <si>
+    <t>I can't believe how much we still have to learn about the universe.</t>
+  </si>
+  <si>
+    <t>That's amazing! I can't believe we can detect such a faint signal from across the universe.</t>
+  </si>
+  <si>
+    <t>That's incredible! I didn't even realize it was possible to detect gravitational waves.</t>
+  </si>
+  <si>
+    <t>That's amazing! I didn't even know that was possible.</t>
+  </si>
+  <si>
+    <t>I'm surprised you're not more excited about it.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000176-0002</t>
+  </si>
+  <si>
+    <t>No, just a pot for the pasta and a pan for the sauce.</t>
+  </si>
+  <si>
+    <t>Great, I'm ready to give it a try.</t>
+  </si>
+  <si>
+    <t>Let me know how it turns out! I'm happy to help if you need any guidance.</t>
+  </si>
+  <si>
+    <t>Let's begin by boiling the pasta, and then we can make the sauce.</t>
+  </si>
+  <si>
+    <t>Sounds like a perfect recipe for a beginner. I'm excited to try it out.</t>
+  </si>
+  <si>
+    <t>Sounds like a great meal. I'm excited to hear how it turns out.</t>
   </si>
   <si>
     <t>SFTANNO-000018-0002</t>
@@ -623,67 +644,67 @@
     <t>Yes, it's fascinating how much we're learning about the universe. It's so exciting!</t>
   </si>
   <si>
-    <t>SFTANNO-000116-0002</t>
-  </si>
-  <si>
-    <t>I haven't had any luck with staffing agencies, and my family doesn't have any recommendations. It's frustrating.</t>
-  </si>
-  <si>
-    <t>It's scary to think about not having a nurse for an extended period of time. Do you have any backups in mind?</t>
-  </si>
-  <si>
-    <t>It's understandable that you're concerned. It's important to find someone you can trust. Have you thought about looking for a nurse with a specialization in your condition?</t>
-  </si>
-  <si>
-    <t>I'm afraid that if you don't find someone soon, it could have negative consequences for your health.</t>
-  </si>
-  <si>
-    <t>It's concerning that you haven't found anyone yet. I hope you can find someone soon.</t>
-  </si>
-  <si>
-    <t>I can understand why you're feeling overwhelmed. It's scary to not have a trusted nurse. Have you considered hiring a private nurse?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000193-0002</t>
-  </si>
-  <si>
-    <t>That's a great idea! I hate the thought of all of my things just going to waste.</t>
-  </si>
-  <si>
-    <t>It's infuriating that we live in a culture that promotes consumerism and waste instead of sustainability and upcycling.</t>
-  </si>
-  <si>
-    <t>We should all do our part to reduce waste and take care of our planet.</t>
-  </si>
-  <si>
-    <t>It's frustrating that our society is so wasteful and doesn't value the resources we have.</t>
-  </si>
-  <si>
-    <t>It's so frustrating that our consumerist society encourages us to constantly buy new things instead of reusing and upcycling.</t>
-  </si>
-  <si>
-    <t>It's frustrating that our society values new things over upcycling and repurposing.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000138-0002</t>
-  </si>
-  <si>
-    <t>What if I get lost in a new city and can't find my way back to my hotel?</t>
-  </si>
-  <si>
-    <t>But it's also a good excuse to explore and see new things. Maybe even try walking around without a map and seeing where it takes you.</t>
-  </si>
-  <si>
-    <t>Have you thought about taking a guided walking tour or using a GPS device to navigate around?</t>
-  </si>
-  <si>
-    <t>I've never had that happen, but it's good to be prepared. Have you thought about carrying a map or using a GPS?</t>
-  </si>
-  <si>
-    <t>Have you tried downloading city maps or using GPS to help navigate?</t>
-  </si>
-  <si>
-    <t>I'm surprised you're not more worried about it, but I'm here to help if you need it.</t>
+    <t>SFTANNO-000108-0002</t>
+  </si>
+  <si>
+    <t>Does it always have to be so muggy and humid after a rain like this?</t>
+  </si>
+  <si>
+    <t>It's infuriating how every time it rains, the humidity level skyrockets.</t>
+  </si>
+  <si>
+    <t>It's so frustrating when the weather feels unbearable for days on end.</t>
+  </si>
+  <si>
+    <t>And don't even get me started on how hard it is to dry our clothes after a rain like this.</t>
+  </si>
+  <si>
+    <t>It's frustrating how long it takes for the weather to go back to normal.</t>
+  </si>
+  <si>
+    <t>And don't even get me started on the mold and mildew that can grow in this weather.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000147-0002</t>
+  </si>
+  <si>
+    <t>Yes, I switched to a new service and they've been fantastic so far.</t>
+  </si>
+  <si>
+    <t>I'm glad you found a good one, but it's frustrating that you had to go through the hassle of finding the right one.</t>
+  </si>
+  <si>
+    <t>It's frustrating that you had to go through all that hassle, but I'm glad you found a new service that works for you.</t>
+  </si>
+  <si>
+    <t>It's ridiculous that you had to go through all that trouble to find a good service.</t>
+  </si>
+  <si>
+    <t>I had a bad experience with a cleaner once too, they left a mess behind and didn't show up for a week.</t>
+  </si>
+  <si>
+    <t>I can't stand when cleaners are unprofessional, it's important to hold them accountable.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000065-0002</t>
+  </si>
+  <si>
+    <t>I fear that our votes won't make a real difference.</t>
+  </si>
+  <si>
+    <t>It's infuriating that our voices might not be heard, but we must keep fighting for change.</t>
+  </si>
+  <si>
+    <t>It's frustrating that some people dismiss the importance of voting.</t>
+  </si>
+  <si>
+    <t>It's maddening that some people think their vote won't matter.</t>
+  </si>
+  <si>
+    <t>It's infuriating that people don't see the power in their vote.</t>
+  </si>
+  <si>
+    <t>It's infuriating that some people dismiss the importance of voting.</t>
   </si>
   <si>
     <t>SFTANNO-000066-0002</t>
@@ -707,67 +728,67 @@
     <t>It's heartbreaking to think about how many people will be affected by this.</t>
   </si>
   <si>
-    <t>SFTANNO-000136-0002</t>
-  </si>
-  <si>
-    <t>I missed out on a snorkeling adventure because of bad weather.</t>
-  </si>
-  <si>
-    <t>I went snorkeling in the Maldives a few years ago, it was so beautiful.</t>
-  </si>
-  <si>
-    <t>I'm sure there are still so many other things to see and do on your trip, just enjoy every moment.</t>
-  </si>
-  <si>
-    <t>But don't worry, there will be plenty of other opportunities to go snorkeling.</t>
-  </si>
-  <si>
-    <t>I went on a snorkeling adventure in the Caribbean last year, it was amazing.</t>
-  </si>
-  <si>
-    <t>But on the bright side, you can always plan for another trip and hopefully have better weather.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000085-0002</t>
-  </si>
-  <si>
-    <t>I found a schedule online that I'm going to try.</t>
-  </si>
-  <si>
-    <t>Honestly, I can't wait to be done with running. It's just so monotonous.</t>
-  </si>
-  <si>
-    <t>Just be careful not to overdo it and hurt yourself, running can be tough on the body.</t>
-  </si>
-  <si>
-    <t>Just make sure to listen to your body and take rest days when you need them.</t>
-  </si>
-  <si>
-    <t>You're going to crush it! Remember to stay consistent and take care of your body.</t>
-  </si>
-  <si>
-    <t>Just be careful with your form, I've heard some people can get injured if they don't have the right technique.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000146-0002</t>
-  </si>
-  <si>
-    <t>I've started buying products with minimal packaging.</t>
-  </si>
-  <si>
-    <t>It's frustrating how companies prioritize packaging over sustainability. Have you tried contacting companies to ask for more sustainable packaging options?</t>
-  </si>
-  <si>
-    <t>It's really frustrating how companies prioritize packaging over sustainability.</t>
-  </si>
-  <si>
-    <t>It's disgusting how much packaging is used in retail. Have you tried buying in bulk to reduce packaging waste?</t>
-  </si>
-  <si>
-    <t>It's really disgusting that some companies prioritize profit over the environment. It's important to support companies that prioritize sustainability.</t>
-  </si>
-  <si>
-    <t>It's disgusting how much unnecessary packaging is used in the retail industry.</t>
+    <t>SFTANNO-000097-0002</t>
+  </si>
+  <si>
+    <t>I just saw a celebrity on the train!</t>
+  </si>
+  <si>
+    <t>I don't know if I would have the courage to talk to them, but that must have been exciting.</t>
+  </si>
+  <si>
+    <t>Oh my gosh, I would have freaked out if I had seen them. I'm not sure I could handle that.</t>
+  </si>
+  <si>
+    <t>But also kind of intimidating, I hope they don't mind us staring at them.</t>
+  </si>
+  <si>
+    <t>I would be terrified if I saw a celebrity on the train, they must get so much attention.</t>
+  </si>
+  <si>
+    <t>I hope they don't recognize me and cause a scene.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000112-0002</t>
+  </si>
+  <si>
+    <t>Yes, please, and thanks for your help.</t>
+  </si>
+  <si>
+    <t>But remember, it's important to read the policy thoroughly to avoid any surprises or hidden costs.</t>
+  </si>
+  <si>
+    <t>But please remember, even with insurance, healthcare can be expensive. Make sure to plan and budget accordingly.</t>
+  </si>
+  <si>
+    <t>Just remember, it's important to research thoroughly and choose the right plan for your needs.</t>
+  </si>
+  <si>
+    <t>Remember, healthcare is important, and I hope you're able to find a plan that works for you.</t>
+  </si>
+  <si>
+    <t>Just make sure to do your research and read the fine print before choosing a plan.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000104-0002</t>
+  </si>
+  <si>
+    <t>I haven't, but I'm definitely looking into it.</t>
+  </si>
+  <si>
+    <t>I'm sorry you had to go through that experience, but I'm glad you're taking steps to protect yourself and find a more welcoming community.</t>
+  </si>
+  <si>
+    <t>It's unfortunate that we have to actively seek out communities that prioritize respect and inclusivity, but it's important to prioritize our own well-being.</t>
+  </si>
+  <si>
+    <t>It's sad that online spaces can be so toxic sometimes. But there are still many wonderful communities out there.</t>
+  </si>
+  <si>
+    <t>It's sad that such behavior exists, but we can make a difference by supporting and creating positive spaces.</t>
+  </si>
+  <si>
+    <t>It's so sad that there are people who use online spaces to spread negativity and hate.</t>
   </si>
   <si>
     <t>SFTANNO-000006-0002</t>
@@ -812,130 +833,130 @@
     <t>I'm interested in learning more about it. Do you have any sources you recommend?</t>
   </si>
   <si>
-    <t>SFTANNO-000127-0002</t>
-  </si>
-  <si>
-    <t>Yeah, I might try some new lilies. But it's still disheartening.</t>
-  </si>
-  <si>
-    <t>I'm surprised you're considering lilies. They're so vibrant! I'm excited to see what you end up with.</t>
-  </si>
-  <si>
-    <t>I just discovered a beautiful bluebell plant at the nursery yesterday. Have you ever grown bluebells?</t>
-  </si>
-  <si>
-    <t>But, have you ever tried growing succulents? They're pretty low-maintenance and can thrive in challenging conditions.</t>
-  </si>
-  <si>
-    <t>Oh, I didn't realize you liked lilies! I have some extra bulbs, and I'd be happy to share them with you.</t>
-  </si>
-  <si>
-    <t>Lilies are such a beautiful choice! I can't wait to see how they turn out.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000083-0002</t>
-  </si>
-  <si>
-    <t>I don't know about predictions, but I'm looking forward to watching some great baseball in the postseason.</t>
-  </si>
-  <si>
-    <t>It's always a great time of year, I can't wait to see what happens.</t>
-  </si>
-  <si>
-    <t>It's going to be a great postseason, I'm excited to see what happens.</t>
-  </si>
-  <si>
-    <t>It's one of the best parts of the baseball season.</t>
-  </si>
-  <si>
-    <t>It's always great to see the best teams compete in the postseason, I can't wait to see who will come out on top.</t>
-  </si>
-  <si>
-    <t>I'm excited to see how the playoffs turn out. It's always a great time for baseball fans.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000012-0002</t>
-  </si>
-  <si>
-    <t>It's sickening to hear about poachers targeting endangered species for their valuable parts.</t>
-  </si>
-  <si>
-    <t>It's heartbreaking to see such a demand for animal parts that's fueling the poaching industry.</t>
-  </si>
-  <si>
-    <t>It's heartbreaking to see these beautiful creatures targeted and killed for profit.</t>
-  </si>
-  <si>
-    <t>It's a sad reality that some people will stop at nothing to profit from the suffering of others.</t>
-  </si>
-  <si>
-    <t>We must do everything in our power to protect these animals and bring the perpetrators to justice.</t>
-  </si>
-  <si>
-    <t>The loss of these animals is a tragedy, and we must do everything we can to protect them.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000081-0002</t>
-  </si>
-  <si>
-    <t>That's a great idea, but it's infuriating that it has to come to this.</t>
-  </si>
-  <si>
-    <t>Let's make a positive change. We can make a difference in our community.</t>
-  </si>
-  <si>
-    <t>I'm genuinely happy we can take action. It's the first step towards a cleaner neighborhood.</t>
-  </si>
-  <si>
-    <t>This event will bring our community together, and I'm excited to be a part of it.</t>
-  </si>
-  <si>
-    <t>I'm thrilled we're taking action. Let's organize the cleanup event and bring happiness back to our neighborhood.</t>
-  </si>
-  <si>
-    <t>But it's a step in the right direction. We can make a difference together.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000151-0002</t>
-  </si>
-  <si>
-    <t>I made a mistake on this project, and I don't have enough yarn to undo it and start again.</t>
-  </si>
-  <si>
-    <t>I have an idea to fix the mistake without using extra yarn. Let's give it a try!</t>
-  </si>
-  <si>
-    <t>It's amazing what a little creativity can do. We'll find a way to fix it.</t>
-  </si>
-  <si>
-    <t>Let's use the yarn we have to create a unique design element instead of undoing the whole project.</t>
-  </si>
-  <si>
-    <t>We'll get creative and see if we can find a way to make it work.</t>
-  </si>
-  <si>
-    <t>Sometimes, mistakes can lead to creative solutions. We'll make it work.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000179-0002</t>
-  </si>
-  <si>
-    <t>I actually haven't. Do you have any recommendations?</t>
-  </si>
-  <si>
-    <t>Let's give it a try sometime. I'm sure we'll both enjoy it.</t>
-  </si>
-  <si>
-    <t>It's really sad that we don't have more options like that around here.</t>
-  </si>
-  <si>
-    <t>I'm sorry I don't have more affordable options to recommend. Maybe we can try something else instead.</t>
-  </si>
-  <si>
-    <t>I'm so sorry to hear that about the other place. I hope you'll enjoy La Piazza though.</t>
-  </si>
-  <si>
-    <t>It's a shame that it's closed right now, but we can keep our eyes peeled for other options.</t>
+    <t>SFTANNO-000110-0002</t>
+  </si>
+  <si>
+    <t>Yeah, I watched a tornado make landfall and destroy an entire neighborhood. It was heartbreaking.</t>
+  </si>
+  <si>
+    <t>It's so sad that something as natural as a tornado can cause so much destruction and loss.</t>
+  </si>
+  <si>
+    <t>It's so devastating to see the destruction and loss of life that tornadoes can cause.</t>
+  </si>
+  <si>
+    <t>I'm so sorry you had to go through that. It's really heartbreaking.</t>
+  </si>
+  <si>
+    <t>It's so sad that tornadoes can cause so much destruction and heartache.</t>
+  </si>
+  <si>
+    <t>It's so sad to think about the destruction and loss of life that tornadoes can cause.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000063-0002</t>
+  </si>
+  <si>
+    <t>I'm happy to see more political discussions in our community.</t>
+  </si>
+  <si>
+    <t>It's about time. The apathy in the past was infuriating.</t>
+  </si>
+  <si>
+    <t>It's fantastic, but it's frustrating when some refuse to engage.</t>
+  </si>
+  <si>
+    <t>But, we need to ensure that these discussions are respectful and not divisive.</t>
+  </si>
+  <si>
+    <t>It's great, but we need to address the polarization. It's dividing us.</t>
+  </si>
+  <si>
+    <t>While it's good, the polarization is disheartening. We need more unity.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000003-0002</t>
+  </si>
+  <si>
+    <t>I have, but the thought of using someone else's lens disgusts me a little.</t>
+  </si>
+  <si>
+    <t>I'm surprised that you've been using the same lens for so long, that's impressive!</t>
+  </si>
+  <si>
+    <t>It's surprising how much hygiene can matter when using someone else's equipment.</t>
+  </si>
+  <si>
+    <t>I'm surprised you wouldn't consider renting a lens, it can be a cost-effective way to try out different lenses.</t>
+  </si>
+  <si>
+    <t>I'm surprised you'd consider using someone else's lens.</t>
+  </si>
+  <si>
+    <t>I'm surprised you haven't tried renting a lens before.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000172-0002</t>
+  </si>
+  <si>
+    <t>I've tried to explain, but it's disheartening when they don't even want to listen.</t>
+  </si>
+  <si>
+    <t>I'm surprised by their lack of openness. Have you considered sharing resources with them?</t>
+  </si>
+  <si>
+    <t>It's surprising how resistant some can be to new ideas. How do you approach those who dismiss mindfulness?</t>
+  </si>
+  <si>
+    <t>It's surprising how little some people are willing to listen. Have you considered sharing your experiences on social media?</t>
+  </si>
+  <si>
+    <t>It's surprising that they don't want to explore the benefits. How do you cope with their skepticism?</t>
+  </si>
+  <si>
+    <t>It's surprising how difficult it can be to change someone's perspective.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000087-0002</t>
+  </si>
+  <si>
+    <t>Can you believe the other team won with that cheap shot?</t>
+  </si>
+  <si>
+    <t>But don't worry, we'll come back stronger next time!</t>
+  </si>
+  <si>
+    <t>But we still won the game, so it doesn't really matter in the end.</t>
+  </si>
+  <si>
+    <t>I'm so happy we won the game despite all the unfair calls. It was such a great win.</t>
+  </si>
+  <si>
+    <t>But on a positive note, our team played really well, despite the loss.</t>
+  </si>
+  <si>
+    <t>But hey, we still have a chance to make it to the finals.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000133-0002</t>
+  </si>
+  <si>
+    <t>I recently learned about a beautiful hiking trail in Norway that I'm dying to see.</t>
+  </si>
+  <si>
+    <t>It's frustrating that I haven't had the chance to explore more of the world yet.</t>
+  </si>
+  <si>
+    <t>It's so frustrating that there are so many incredible places in the world to see, and we only have so much time to see them all.</t>
+  </si>
+  <si>
+    <t>It's frustrating that I haven't had the chance to travel as much as I want to.</t>
+  </si>
+  <si>
+    <t>It's frustrating when we discover something amazing but can't immediately go see it for ourselves.</t>
+  </si>
+  <si>
+    <t>It's frustrating that some of the most beautiful places in the world are only accessible to those who can afford to travel.</t>
   </si>
   <si>
     <t>SFTANNO-000011-0002</t>
@@ -983,25 +1004,58 @@
     <t>USER_EMOTION</t>
   </si>
   <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Fear</t>
+  </si>
+  <si>
+    <t>Sadness</t>
+  </si>
+  <si>
     <t>Happiness</t>
   </si>
   <si>
-    <t>Fear</t>
-  </si>
-  <si>
-    <t>Neutral</t>
+    <t>Surprise</t>
+  </si>
+  <si>
+    <t>Al ser texto es dificil saber la emoción. Ayuda un poco el hecho de que ciertas palabras aparezcan. El uso de signos de puntuación también podría ayudar</t>
+  </si>
+  <si>
+    <t>En el modelo 3 hay dos emociones: felicidad y miedo. En las otras me decanto por el mideo porque no expresa tanta felicidad.</t>
   </si>
   <si>
     <t>Disgust</t>
   </si>
   <si>
-    <t>Surprise</t>
-  </si>
-  <si>
-    <t>Sadness</t>
-  </si>
-  <si>
     <t>Anger</t>
+  </si>
+  <si>
+    <t>falta contexto</t>
+  </si>
+  <si>
+    <t>La emoción del modelo 2 no me parece incluida en la lista. Es como si fuera ironía y a la vez optimismo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En el modelo 5 comento ira, pero es más por el tono serio de la frase. </t>
+  </si>
+  <si>
+    <t>Ira por el tono serio. Muy diferente a las respuestas de los modelos 4 y 5</t>
+  </si>
+  <si>
+    <t>Varias emociones a la vez. Me decanto por neutral</t>
+  </si>
+  <si>
+    <t>Hay varias emociones. Dificil elección</t>
+  </si>
+  <si>
+    <t>Hay dos emociones. Una de tristeza al principio y la otra optimista. No creo que Neutral sea la solución</t>
+  </si>
+  <si>
+    <t>La respuesta del modelo 2 no es congruente</t>
+  </si>
+  <si>
+    <t>falta contexto. Son raras las respuestas del 3 y 4</t>
   </si>
 </sst>
 </file>
@@ -1057,7 +1111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1065,14 +1119,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1376,1877 +1424,1973 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N45"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N46"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="0" style="2" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="28.140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="16" style="4" customWidth="1"/>
-    <col min="4" max="4" width="28.140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16" style="4" customWidth="1"/>
-    <col min="6" max="6" width="28.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="16" style="4" customWidth="1"/>
-    <col min="8" max="8" width="28.140625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="16" style="4" customWidth="1"/>
-    <col min="10" max="10" width="28.140625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="16" style="4" customWidth="1"/>
-    <col min="12" max="12" width="28.140625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="16" style="4" customWidth="1"/>
-    <col min="14" max="14" width="28.140625" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.109375" style="3"/>
+    <col min="2" max="14" width="28.33203125" style="3" customWidth="1"/>
+    <col min="15" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>321</v>
+      <c r="C1" s="1" t="s">
+        <v>328</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="120" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>322</v>
+      <c r="C2" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>323</v>
+      <c r="E2" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>324</v>
+      <c r="G2" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>324</v>
+      <c r="I2" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="5" t="s">
-        <v>324</v>
+      <c r="K2" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="5" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="M2" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="N2" s="2"/>
+    </row>
+    <row r="3" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>323</v>
+      <c r="C3" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>323</v>
+      <c r="E3" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>323</v>
+      <c r="G3" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>323</v>
+      <c r="I3" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="5" t="s">
-        <v>323</v>
+      <c r="K3" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="5" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="M3" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="N3" s="2"/>
+    </row>
+    <row r="4" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>325</v>
+      <c r="C4" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>326</v>
+      <c r="E4" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>326</v>
+      <c r="G4" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>326</v>
+      <c r="I4" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="K4" s="5" t="s">
-        <v>324</v>
+      <c r="K4" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="M4" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="M4" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>327</v>
+      <c r="C5" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="5" t="s">
-        <v>327</v>
+      <c r="E5" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>327</v>
+      <c r="G5" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>324</v>
+      <c r="I5" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K5" s="5" t="s">
-        <v>324</v>
+      <c r="K5" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="M5" s="5" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+      <c r="M5" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>323</v>
+      <c r="C6" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>324</v>
+      <c r="E6" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>324</v>
+      <c r="G6" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>324</v>
+      <c r="I6" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="K6" s="5" t="s">
-        <v>324</v>
+      <c r="K6" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="M6" s="5" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+      <c r="M6" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="N6" s="2"/>
+    </row>
+    <row r="7" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>324</v>
+      <c r="C7" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>323</v>
+      <c r="E7" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>323</v>
+      <c r="G7" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>323</v>
+      <c r="I7" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="K7" s="5" t="s">
-        <v>323</v>
+      <c r="K7" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="M7" s="5" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+      <c r="M7" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>324</v>
+      <c r="C8" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>326</v>
+      <c r="E8" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>326</v>
+      <c r="G8" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>326</v>
+      <c r="I8" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>326</v>
+      <c r="K8" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="M8" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="M8" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="N8" s="2"/>
+    </row>
+    <row r="9" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>62</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>328</v>
+      <c r="C9" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>324</v>
+      <c r="E9" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>324</v>
+      <c r="G9" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>324</v>
+      <c r="I9" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="K9" s="5" t="s">
-        <v>324</v>
+      <c r="K9" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M9" s="5" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+      <c r="M9" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="N9" s="2"/>
+    </row>
+    <row r="10" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>69</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>327</v>
+      <c r="C10" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>323</v>
+      <c r="E10" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>323</v>
+      <c r="G10" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>323</v>
+      <c r="I10" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="K10" s="5" t="s">
-        <v>323</v>
+      <c r="K10" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="M10" s="5" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+      <c r="M10" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="N10" s="2"/>
+    </row>
+    <row r="11" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>76</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>323</v>
+      <c r="C11" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>326</v>
+      <c r="E11" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>326</v>
+      <c r="G11" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="I11" s="5" t="s">
-        <v>326</v>
+      <c r="I11" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="K11" s="5" t="s">
-        <v>326</v>
+      <c r="K11" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M11" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+      <c r="M11" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="N11" s="2"/>
+    </row>
+    <row r="12" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>83</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>323</v>
+      <c r="C12" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>324</v>
+      <c r="E12" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>324</v>
+      <c r="G12" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="I12" s="5" t="s">
-        <v>324</v>
+      <c r="I12" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="K12" s="5" t="s">
-        <v>324</v>
+      <c r="K12" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="M12" s="5" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+      <c r="M12" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>324</v>
+      <c r="C13" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>324</v>
+      <c r="E13" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>324</v>
+      <c r="G13" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="I13" s="5" t="s">
-        <v>324</v>
+      <c r="I13" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="K13" s="5" t="s">
-        <v>324</v>
+      <c r="K13" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="M13" s="5" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+      <c r="M13" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>97</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>323</v>
+      <c r="C14" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>325</v>
+      <c r="E14" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>325</v>
+      <c r="G14" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="I14" s="5" t="s">
-        <v>325</v>
+      <c r="I14" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="K14" s="5" t="s">
-        <v>325</v>
+      <c r="K14" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="M14" s="5" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+      <c r="M14" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>328</v>
+      <c r="C15" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>324</v>
+      <c r="E15" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>327</v>
+      <c r="G15" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="I15" s="5" t="s">
-        <v>327</v>
+      <c r="I15" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="K15" s="5" t="s">
-        <v>327</v>
+      <c r="K15" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="M15" s="5" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+      <c r="M15" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="N15" s="2"/>
+    </row>
+    <row r="16" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>111</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>325</v>
+      <c r="C16" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>322</v>
+      <c r="E16" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>322</v>
+      <c r="G16" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="I16" s="5" t="s">
-        <v>322</v>
+      <c r="I16" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="K16" s="5" t="s">
-        <v>322</v>
+      <c r="K16" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="M16" s="5" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="M16" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="N16" s="2"/>
+    </row>
+    <row r="17" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>118</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>326</v>
+      <c r="C17" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>327</v>
+      <c r="E17" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>325</v>
+      <c r="G17" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="I17" s="5" t="s">
-        <v>326</v>
+      <c r="I17" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="K17" s="5" t="s">
-        <v>326</v>
+      <c r="K17" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="M17" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="M17" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>324</v>
+      <c r="C18" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>324</v>
+      <c r="E18" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>324</v>
+      <c r="G18" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="I18" s="5" t="s">
-        <v>325</v>
+      <c r="I18" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="K18" s="5" t="s">
-        <v>325</v>
+      <c r="K18" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="M18" s="5" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="M18" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>322</v>
+      <c r="C19" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>326</v>
+      <c r="E19" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>326</v>
+      <c r="G19" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="I19" s="5" t="s">
-        <v>326</v>
+      <c r="I19" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="K19" s="5" t="s">
-        <v>326</v>
+      <c r="K19" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="M19" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="M19" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="N19" s="2"/>
+    </row>
+    <row r="20" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>139</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>327</v>
+      <c r="C20" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>323</v>
+      <c r="E20" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>323</v>
+      <c r="G20" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="I20" s="5" t="s">
-        <v>323</v>
+      <c r="I20" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="K20" s="5" t="s">
-        <v>323</v>
+      <c r="K20" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="M20" s="5" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="M20" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="N20" s="2"/>
+    </row>
+    <row r="21" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>146</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>322</v>
+      <c r="C21" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>322</v>
+      <c r="E21" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>322</v>
+      <c r="G21" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="I21" s="5" t="s">
-        <v>322</v>
+      <c r="I21" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="K21" s="5" t="s">
-        <v>322</v>
+      <c r="K21" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="M21" s="5" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="M21" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="N21" s="2"/>
+    </row>
+    <row r="22" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>153</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>324</v>
+      <c r="C22" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>322</v>
+      <c r="E22" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>322</v>
+      <c r="G22" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="I22" s="5" t="s">
-        <v>322</v>
+      <c r="I22" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="K22" s="5" t="s">
-        <v>322</v>
+      <c r="K22" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="M22" s="5" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="M22" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>160</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>325</v>
+      <c r="C23" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>325</v>
+      <c r="E23" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>325</v>
+      <c r="G23" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="I23" s="5" t="s">
-        <v>325</v>
+      <c r="I23" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="K23" s="5" t="s">
-        <v>325</v>
+      <c r="K23" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="M23" s="5" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="M23" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="N23" s="2"/>
+    </row>
+    <row r="24" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>167</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>327</v>
+      <c r="C24" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>323</v>
+      <c r="E24" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>327</v>
+      <c r="G24" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="I24" s="5" t="s">
-        <v>325</v>
+      <c r="I24" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="K24" s="5" t="s">
-        <v>325</v>
+      <c r="K24" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="M24" s="5" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="M24" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="N24" s="2"/>
+    </row>
+    <row r="25" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>174</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>326</v>
+      <c r="C25" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>325</v>
+      <c r="E25" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>325</v>
+      <c r="G25" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="I25" s="5" t="s">
-        <v>325</v>
+      <c r="I25" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="K25" s="5" t="s">
-        <v>327</v>
+      <c r="K25" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="M25" s="5" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="M25" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>181</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>322</v>
+      <c r="C26" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>322</v>
+      <c r="E26" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>322</v>
+      <c r="G26" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="I26" s="5" t="s">
-        <v>322</v>
+      <c r="I26" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="K26" s="5" t="s">
-        <v>322</v>
+      <c r="K26" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="M26" s="5" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="M26" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="N26" s="2"/>
+    </row>
+    <row r="27" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>188</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>322</v>
+      <c r="C27" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>326</v>
+      <c r="E27" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>326</v>
+      <c r="G27" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="I27" s="5" t="s">
-        <v>326</v>
+      <c r="I27" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="K27" s="5" t="s">
-        <v>326</v>
+      <c r="K27" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="M27" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="M27" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="N27" s="2"/>
+    </row>
+    <row r="28" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>195</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>326</v>
+      <c r="C28" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>326</v>
+      <c r="E28" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="G28" s="5" t="s">
-        <v>326</v>
+      <c r="G28" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="I28" s="5" t="s">
-        <v>326</v>
+      <c r="I28" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="K28" s="5" t="s">
-        <v>326</v>
+      <c r="K28" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="M28" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+      <c r="M28" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="N28" s="2"/>
+    </row>
+    <row r="29" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>202</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>328</v>
+      <c r="C29" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>323</v>
+      <c r="E29" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>324</v>
+      <c r="G29" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="I29" s="5" t="s">
-        <v>323</v>
+      <c r="I29" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="K29" s="5" t="s">
-        <v>327</v>
+      <c r="K29" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="M29" s="5" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="M29" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="N29" s="2"/>
+    </row>
+    <row r="30" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>209</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>322</v>
+      <c r="C30" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>328</v>
+      <c r="E30" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>324</v>
+      <c r="G30" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="I30" s="5" t="s">
-        <v>328</v>
+      <c r="I30" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="K30" s="5" t="s">
-        <v>328</v>
+      <c r="K30" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="M30" s="5" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="M30" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="N30" s="2"/>
+    </row>
+    <row r="31" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>216</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>324</v>
+      <c r="C31" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>322</v>
+      <c r="E31" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>324</v>
+      <c r="G31" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="I31" s="5" t="s">
-        <v>324</v>
+      <c r="I31" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="K31" s="5" t="s">
-        <v>324</v>
+      <c r="K31" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="M31" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="M31" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="N31" s="2"/>
+    </row>
+    <row r="32" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>223</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>327</v>
+      <c r="C32" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>325</v>
+      <c r="E32" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>325</v>
+      <c r="G32" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="I32" s="5" t="s">
-        <v>325</v>
+      <c r="I32" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="K32" s="5" t="s">
-        <v>325</v>
+      <c r="K32" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="M32" s="5" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="M32" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="N32" s="2"/>
+    </row>
+    <row r="33" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>230</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>325</v>
+      <c r="C33" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>322</v>
+      <c r="E33" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>322</v>
+      <c r="G33" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="I33" s="5" t="s">
-        <v>322</v>
+      <c r="I33" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="K33" s="5" t="s">
-        <v>322</v>
+      <c r="K33" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="M33" s="5" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="M33" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="N33" s="2"/>
+    </row>
+    <row r="34" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>237</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>324</v>
+      <c r="C34" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>324</v>
+      <c r="E34" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="G34" s="5" t="s">
-        <v>324</v>
+      <c r="G34" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="I34" s="5" t="s">
-        <v>324</v>
+      <c r="I34" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="K34" s="5" t="s">
-        <v>324</v>
+      <c r="K34" s="2" t="s">
+        <v>330</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="M34" s="5" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+      <c r="M34" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="N34" s="2"/>
+    </row>
+    <row r="35" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>244</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>324</v>
+      <c r="C35" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="E35" s="5" t="s">
-        <v>325</v>
+      <c r="E35" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="G35" s="5" t="s">
-        <v>325</v>
+      <c r="G35" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="I35" s="5" t="s">
-        <v>325</v>
+      <c r="I35" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="K35" s="5" t="s">
-        <v>325</v>
+      <c r="K35" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="M35" s="5" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="M35" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="N35" s="2"/>
+    </row>
+    <row r="36" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>251</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>328</v>
+      <c r="C36" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="E36" s="5" t="s">
-        <v>328</v>
+      <c r="E36" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="G36" s="5" t="s">
-        <v>328</v>
+      <c r="G36" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="I36" s="5" t="s">
-        <v>328</v>
+      <c r="I36" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="K36" s="5" t="s">
-        <v>328</v>
+      <c r="K36" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="M36" s="5" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="M36" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="N36" s="2"/>
+    </row>
+    <row r="37" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>258</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C37" s="5" t="s">
-        <v>324</v>
+      <c r="C37" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="E37" s="5" t="s">
-        <v>324</v>
+      <c r="E37" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="G37" s="5" t="s">
-        <v>322</v>
+      <c r="G37" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="I37" s="5" t="s">
-        <v>322</v>
+      <c r="I37" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="K37" s="5" t="s">
-        <v>322</v>
+      <c r="K37" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="M37" s="5" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="M37" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="N37" s="2"/>
+    </row>
+    <row r="38" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>265</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="C38" s="5" t="s">
-        <v>327</v>
+      <c r="C38" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="E38" s="5" t="s">
-        <v>326</v>
+      <c r="E38" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="G38" s="5" t="s">
-        <v>324</v>
+      <c r="G38" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="I38" s="5" t="s">
-        <v>324</v>
+      <c r="I38" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="K38" s="5" t="s">
-        <v>322</v>
+      <c r="K38" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="M38" s="5" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="M38" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>272</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>322</v>
+      <c r="C39" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="E39" s="5" t="s">
-        <v>322</v>
+      <c r="E39" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="G39" s="5" t="s">
-        <v>322</v>
+      <c r="G39" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="I39" s="5" t="s">
-        <v>322</v>
+      <c r="I39" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="K39" s="5" t="s">
-        <v>322</v>
+      <c r="K39" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="M39" s="5" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="M39" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="N39" s="2"/>
+    </row>
+    <row r="40" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>279</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>325</v>
+      <c r="C40" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>327</v>
+      <c r="E40" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="G40" s="5" t="s">
-        <v>327</v>
+      <c r="G40" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="I40" s="5" t="s">
-        <v>327</v>
+      <c r="I40" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="K40" s="5" t="s">
-        <v>328</v>
+      <c r="K40" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="M40" s="5" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="M40" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="N40" s="2"/>
+    </row>
+    <row r="41" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>286</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C41" s="5" t="s">
-        <v>328</v>
+      <c r="C41" s="2" t="s">
+        <v>336</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="E41" s="5" t="s">
-        <v>322</v>
+      <c r="E41" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="G41" s="5" t="s">
-        <v>322</v>
+      <c r="G41" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="I41" s="5" t="s">
-        <v>322</v>
+      <c r="I41" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="K41" s="5" t="s">
-        <v>322</v>
+      <c r="K41" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="M41" s="5" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="M41" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="N41" s="2"/>
+    </row>
+    <row r="42" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>293</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>325</v>
+      <c r="C42" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="E42" s="5" t="s">
-        <v>322</v>
+      <c r="E42" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="G42" s="5" t="s">
-        <v>322</v>
+      <c r="G42" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="I42" s="5" t="s">
-        <v>322</v>
+      <c r="I42" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="K42" s="5" t="s">
-        <v>322</v>
+      <c r="K42" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="M42" s="5" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="M42" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="N42" s="2"/>
+    </row>
+    <row r="43" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="C43" s="5" t="s">
-        <v>324</v>
+      <c r="C43" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="E43" s="5" t="s">
-        <v>322</v>
+      <c r="E43" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="G43" s="5" t="s">
-        <v>327</v>
+      <c r="G43" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="I43" s="5" t="s">
-        <v>327</v>
+      <c r="I43" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="K43" s="5" t="s">
-        <v>327</v>
+      <c r="K43" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="M43" s="5" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="M43" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="N43" s="2"/>
+    </row>
+    <row r="44" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>307</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>322</v>
+      <c r="C44" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="E44" s="5" t="s">
-        <v>322</v>
+      <c r="E44" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="G44" s="5" t="s">
-        <v>324</v>
+      <c r="G44" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="I44" s="5" t="s">
-        <v>324</v>
+      <c r="I44" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="K44" s="5" t="s">
-        <v>324</v>
+      <c r="K44" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="M44" s="5" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="M44" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>324</v>
+      <c r="C45" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="E45" s="5" t="s">
-        <v>328</v>
+      <c r="E45" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="G45" s="5" t="s">
-        <v>328</v>
+      <c r="G45" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="I45" s="5" t="s">
-        <v>324</v>
+      <c r="I45" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="K45" s="5" t="s">
-        <v>322</v>
+      <c r="K45" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="M45" s="5" t="s">
-        <v>328</v>
-      </c>
+      <c r="M45" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="N46" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G45 K2:K45 I2:I45 E2:E45 C2:C45 M2:M45" xr:uid="{7D0DF561-7046-44C6-B0E7-075ACD1B268E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C46 E2:E46 G2:G46 I2:I46 K2:K46 M2:M46" xr:uid="{23AE58DB-43D3-4610-B7CF-96C69284197E}">
       <formula1>"Anger,Disgust,Fear,Happiness,Sadness,Surprise,Neutral"</formula1>
     </dataValidation>
   </dataValidations>
